--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484548_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484548_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.2913</v>
+        <v>3.3212</v>
       </c>
       <c r="E2" t="n">
-        <v>5.5004</v>
+        <v>3.7285</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.2091</v>
+        <v>-0.4073</v>
       </c>
       <c r="G2" t="n">
         <v>1.0782</v>
@@ -610,13 +610,13 @@
         <v>2.1991</v>
       </c>
       <c r="S2" t="n">
-        <v>3.2027</v>
+        <v>1.2326</v>
       </c>
       <c r="T2" t="n">
-        <v>2.9284</v>
+        <v>1.1565</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2743</v>
+        <v>0.0761</v>
       </c>
       <c r="V2" t="n">
         <v>0.6439</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.3738</v>
+        <v>2.3242</v>
       </c>
       <c r="E3" t="n">
         <v>1.673</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7007</v>
+        <v>0.6512</v>
       </c>
       <c r="G3" t="n">
         <v>2.2862</v>
@@ -688,13 +688,13 @@
         <v>1.6493</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8652</v>
+        <v>0.8156</v>
       </c>
       <c r="T3" t="n">
         <v>0.6395</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2256</v>
+        <v>0.1761</v>
       </c>
       <c r="V3" t="n">
         <v>0.3219</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.045</v>
+        <v>0.2562</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3827</v>
+        <v>0.7673</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3377</v>
+        <v>-0.5111</v>
       </c>
       <c r="G4" t="n">
         <v>0.8085</v>
@@ -766,13 +766,13 @@
         <v>0.1833</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3524</v>
+        <v>-0.1412</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0905</v>
+        <v>0.4751</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4429</v>
+        <v>-0.6163</v>
       </c>
       <c r="V4" t="n">
         <v>0.3219</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. GARCIA MARAVILLA</t>
+          <t>J. YUBERO OJEDA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2064</v>
+        <v>-0.1119</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.8946</v>
+        <v>-0.6688</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6882</v>
+        <v>0.5569</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.0272</v>
+        <v>-0.8266</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1554</v>
+        <v>-1.9452</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1282</v>
+        <v>1.1185</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0217</v>
+        <v>-0.9836</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0217</v>
+        <v>-1.1087</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0489</v>
+        <v>0.157</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1771</v>
+        <v>-0.8365</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1282</v>
+        <v>0.9935</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.9163</v>
+        <v>0.3665</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>0.3665</v>
       </c>
       <c r="S5" t="n">
-        <v>0.114</v>
+        <v>0.3482</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>0.3149</v>
       </c>
       <c r="U5" t="n">
-        <v>0.114</v>
+        <v>0.0334</v>
       </c>
       <c r="V5" t="n">
-        <v>0.6231</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.6231</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. YUBERO OJEDA</t>
+          <t>P. GARCIA MARAVILLA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3815</v>
+        <v>-0.1598</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.7649</v>
+        <v>-0.7985</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3835</v>
+        <v>0.6387</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.8266</v>
+        <v>-0.0272</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.9452</v>
+        <v>-0.1554</v>
       </c>
       <c r="I6" t="n">
-        <v>1.1185</v>
+        <v>0.1282</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.9836</v>
+        <v>0.0217</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.1087</v>
+        <v>0.0217</v>
       </c>
       <c r="L6" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0.157</v>
+        <v>-0.0489</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.8365</v>
+        <v>-0.1771</v>
       </c>
       <c r="O6" t="n">
-        <v>0.9935</v>
+        <v>0.1282</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3665</v>
+        <v>-0.9163</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3665</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.07870000000000001</v>
+        <v>0.1606</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2187</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1401</v>
+        <v>0.0645</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.6231</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>0.6231</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. ARNAIZ VEGA</t>
+          <t>S. ARNAIZ VEGA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.1343</v>
+        <v>-0.7121</v>
       </c>
       <c r="E7" t="n">
-        <v>1.3239</v>
+        <v>2.5635</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.4582</v>
+        <v>-3.2756</v>
       </c>
       <c r="G7" t="n">
-        <v>2.4843</v>
+        <v>0.8478</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.9814</v>
+        <v>3.7713</v>
       </c>
       <c r="I7" t="n">
-        <v>5.4657</v>
+        <v>-2.9236</v>
       </c>
       <c r="J7" t="n">
-        <v>2.48</v>
+        <v>3.6079</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.0564</v>
+        <v>4.8642</v>
       </c>
       <c r="L7" t="n">
-        <v>4.5364</v>
+        <v>-1.2563</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0042</v>
+        <v>-2.7602</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.925</v>
+        <v>-1.0929</v>
       </c>
       <c r="O7" t="n">
-        <v>0.9293</v>
+        <v>-1.6673</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.9163</v>
+        <v>-0.5498</v>
       </c>
       <c r="Q7" t="n">
         <v>-1.8326</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9163</v>
+        <v>1.2828</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1683</v>
+        <v>-0.0547</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6765</v>
+        <v>0.1546</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.8448</v>
+        <v>-0.2093</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.5339</v>
+        <v>-0.9554</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.6335</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.5339</v>
+        <v>-1.5889</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. CORNEJO GONZALEZ</t>
+          <t>A. GONZALEZ SOLER</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.1693</v>
+        <v>-0.8159999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7621</v>
+        <v>-0.3589</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.9314</v>
+        <v>-0.4571</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.4459</v>
+        <v>-0.9125</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.3978</v>
+        <v>-0.9573</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9518</v>
+        <v>0.0449</v>
       </c>
       <c r="J8" t="n">
-        <v>1.667</v>
+        <v>-0.4452</v>
       </c>
       <c r="K8" t="n">
-        <v>0.266</v>
+        <v>-0.5543</v>
       </c>
       <c r="L8" t="n">
-        <v>1.401</v>
+        <v>0.1091</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.113</v>
+        <v>-0.4673</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.6638</v>
+        <v>-0.403</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4492</v>
+        <v>-0.0643</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.4661</v>
+        <v>0.9163</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.7489</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.2828</v>
+        <v>0.9163</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.1578</v>
+        <v>-0.8198</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0565</v>
+        <v>0.0864</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.1012</v>
+        <v>-0.9061</v>
       </c>
       <c r="V8" t="n">
-        <v>1.9005</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.9005</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. GONZALEZ SOLER</t>
+          <t>M. CORNEJO GONZALEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3081</v>
+        <v>-1.0647</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.7024</v>
+        <v>0.8171</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.6057</v>
+        <v>-1.8819</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.9125</v>
+        <v>-0.4459</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.9573</v>
+        <v>-1.3978</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0449</v>
+        <v>0.9518</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.4452</v>
+        <v>1.667</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.5543</v>
+        <v>0.266</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1091</v>
+        <v>1.401</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.4673</v>
+        <v>-2.113</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.403</v>
+        <v>-1.6638</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.0643</v>
+        <v>-0.4492</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9163</v>
+        <v>-1.4661</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-2.7489</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9163</v>
+        <v>1.2828</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.3119</v>
+        <v>-1.0532</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2572</v>
+        <v>-0.0015</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.0548</v>
+        <v>-1.0517</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.9005</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.9005</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. ARNAIZ VEGA</t>
+          <t>J. ARNAIZ VEGA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.3386</v>
+        <v>-1.1809</v>
       </c>
       <c r="E10" t="n">
-        <v>1.9865</v>
+        <v>1.2278</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.3251</v>
+        <v>-2.4087</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8478</v>
+        <v>2.4843</v>
       </c>
       <c r="H10" t="n">
-        <v>3.7713</v>
+        <v>-2.9814</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.9236</v>
+        <v>5.4657</v>
       </c>
       <c r="J10" t="n">
-        <v>3.6079</v>
+        <v>2.48</v>
       </c>
       <c r="K10" t="n">
-        <v>4.8642</v>
+        <v>-2.0564</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.2563</v>
+        <v>4.5364</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.7602</v>
+        <v>0.0042</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.0929</v>
+        <v>-0.925</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.6673</v>
+        <v>0.9293</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.5498</v>
+        <v>-0.9163</v>
       </c>
       <c r="Q10" t="n">
         <v>-1.8326</v>
       </c>
       <c r="R10" t="n">
-        <v>1.2828</v>
+        <v>0.9163</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6812</v>
+        <v>-0.2149</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4223</v>
+        <v>0.5803</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2588</v>
+        <v>-0.7953</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.9554</v>
+        <v>-2.5339</v>
       </c>
       <c r="W10" t="n">
-        <v>0.6335</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.5889</v>
+        <v>-2.5339</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. GONZALEZ FERRER</t>
+          <t>S. DOMINGUEZ ALEIXANDRE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.2172</v>
+        <v>-2.7219</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.053</v>
+        <v>-0.8193</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.1642</v>
+        <v>-1.9026</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.0212</v>
+        <v>-2.5517</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.6237</v>
+        <v>-0.2403</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6025</v>
+        <v>-2.3115</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.5936</v>
+        <v>0.8587</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.2604</v>
+        <v>1.3747</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6667999999999999</v>
+        <v>-0.516</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.4276</v>
+        <v>-3.4104</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.3633</v>
+        <v>-1.6149</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.0643</v>
+        <v>-1.7955</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.733</v>
+        <v>-0.1833</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9163</v>
+        <v>-1.8326</v>
       </c>
       <c r="R11" t="n">
-        <v>0.1833</v>
+        <v>1.6493</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4271</v>
+        <v>0.335</v>
       </c>
       <c r="T11" t="n">
-        <v>1.08</v>
+        <v>0.1546</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6529</v>
+        <v>0.1804</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.89</v>
+        <v>-0.3219</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.6231</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.267</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S. DOMINGUEZ ALEIXANDRE</t>
+          <t>D. GONZALEZ FERRER</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.23</v>
+        <v>-3.8684</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.4513</v>
+        <v>-1.6299</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.7788</v>
+        <v>-2.2385</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.5517</v>
+        <v>-1.0212</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.2403</v>
+        <v>-1.6237</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.3115</v>
+        <v>0.6025</v>
       </c>
       <c r="J12" t="n">
-        <v>0.8587</v>
+        <v>-0.5936</v>
       </c>
       <c r="K12" t="n">
-        <v>1.3747</v>
+        <v>-1.2604</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.516</v>
+        <v>0.6667999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>-3.4104</v>
+        <v>-0.4276</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.6149</v>
+        <v>-0.3633</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.7955</v>
+        <v>-0.0643</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.1833</v>
+        <v>-0.733</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.8326</v>
+        <v>-0.9163</v>
       </c>
       <c r="R12" t="n">
-        <v>1.6493</v>
+        <v>0.1833</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1731</v>
+        <v>-0.2242</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4774</v>
+        <v>0.503</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3043</v>
+        <v>-0.7272</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.3219</v>
+        <v>-1.89</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>-0.6231</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.3219</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.0354</v>
+        <v>-5.3014</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.4671</v>
+        <v>-0.9313</v>
       </c>
       <c r="F13" t="n">
-        <v>-4.5683</v>
+        <v>-4.3701</v>
       </c>
       <c r="G13" t="n">
         <v>-0.5915</v>
@@ -1468,13 +1468,13 @@
         <v>1.2828</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.8391999999999999</v>
+        <v>-0.1052</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4042</v>
+        <v>0.1316</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.435</v>
+        <v>-0.2368</v>
       </c>
       <c r="V13" t="n">
         <v>-2.2224</v>
@@ -1501,22 +1501,22 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-10.3107</v>
+        <v>-10.0355</v>
       </c>
       <c r="E14" t="n">
-        <v>5.295299999999999</v>
+        <v>5.5705</v>
       </c>
       <c r="F14" t="n">
         <v>-15.6061</v>
       </c>
       <c r="G14" t="n">
-        <v>1.128400000000001</v>
+        <v>1.1284</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.7932999999999999</v>
+        <v>-0.7933000000000003</v>
       </c>
       <c r="I14" t="n">
-        <v>1.921499999999999</v>
+        <v>1.9215</v>
       </c>
       <c r="J14" t="n">
         <v>16.6788</v>
@@ -1534,7 +1534,7 @@
         <v>-11.2193</v>
       </c>
       <c r="O14" t="n">
-        <v>-4.3312</v>
+        <v>-4.331199999999999</v>
       </c>
       <c r="P14" t="n">
         <v>-7.330299999999999</v>
@@ -1546,13 +1546,13 @@
         <v>11.9118</v>
       </c>
       <c r="S14" t="n">
-        <v>0.003800000000000026</v>
+        <v>0.2788000000000003</v>
       </c>
       <c r="T14" t="n">
-        <v>4.015999999999999</v>
+        <v>4.2912</v>
       </c>
       <c r="U14" t="n">
-        <v>-4.0123</v>
+        <v>-4.0122</v>
       </c>
       <c r="V14" t="n">
         <v>-4.112299999999999</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. CAMPOS DE BENGOA</t>
+          <t>M. MORAGAS AZNAR</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>8.2234</v>
+        <v>7.3888</v>
       </c>
       <c r="E15" t="n">
-        <v>5.8411</v>
+        <v>8.5785</v>
       </c>
       <c r="F15" t="n">
+        <v>-1.1897</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2.5523</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.8306</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.7217</v>
+      </c>
+      <c r="J15" t="n">
+        <v>5.8955</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3.0837</v>
+      </c>
+      <c r="L15" t="n">
+        <v>2.8119</v>
+      </c>
+      <c r="M15" t="n">
+        <v>-3.3433</v>
+      </c>
+      <c r="N15" t="n">
+        <v>-2.2531</v>
+      </c>
+      <c r="O15" t="n">
+        <v>-1.0902</v>
+      </c>
+      <c r="P15" t="n">
         <v>2.3823</v>
       </c>
-      <c r="G15" t="n">
-        <v>4.0399</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-0.5764</v>
-      </c>
-      <c r="I15" t="n">
-        <v>4.6163</v>
-      </c>
-      <c r="J15" t="n">
-        <v>5.0643</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0.9287</v>
-      </c>
-      <c r="L15" t="n">
-        <v>4.1356</v>
-      </c>
-      <c r="M15" t="n">
-        <v>-1.0244</v>
-      </c>
-      <c r="N15" t="n">
-        <v>-1.5051</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0.4807</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1.0995</v>
-      </c>
       <c r="Q15" t="n">
-        <v>-1.8326</v>
+        <v>-0.9163</v>
       </c>
       <c r="R15" t="n">
-        <v>2.9321</v>
+        <v>3.2986</v>
       </c>
       <c r="S15" t="n">
-        <v>3.0839</v>
+        <v>-0.0694</v>
       </c>
       <c r="T15" t="n">
-        <v>2.2874</v>
+        <v>0.4318</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7966</v>
+        <v>-0.5012</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>2.5235</v>
       </c>
       <c r="W15" t="n">
-        <v>0.3219</v>
+        <v>3.1674</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.3219</v>
+        <v>-0.6439</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. MORAGAS AZNAR</t>
+          <t>J. CAMPOS DE BENGOA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>7.0916</v>
+        <v>6.3395</v>
       </c>
       <c r="E16" t="n">
-        <v>8.289999999999999</v>
+        <v>4.3987</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.1984</v>
+        <v>1.9407</v>
       </c>
       <c r="G16" t="n">
-        <v>2.5523</v>
+        <v>4.0399</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8306</v>
+        <v>-0.5764</v>
       </c>
       <c r="I16" t="n">
-        <v>1.7217</v>
+        <v>4.6163</v>
       </c>
       <c r="J16" t="n">
-        <v>5.8955</v>
+        <v>5.0643</v>
       </c>
       <c r="K16" t="n">
-        <v>3.0837</v>
+        <v>0.9287</v>
       </c>
       <c r="L16" t="n">
-        <v>2.8119</v>
+        <v>4.1356</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.3433</v>
+        <v>-1.0244</v>
       </c>
       <c r="N16" t="n">
-        <v>-2.2531</v>
+        <v>-1.5051</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.0902</v>
+        <v>0.4807</v>
       </c>
       <c r="P16" t="n">
-        <v>2.3823</v>
+        <v>1.0995</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9163</v>
+        <v>-1.8326</v>
       </c>
       <c r="R16" t="n">
-        <v>3.2986</v>
+        <v>2.9321</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3665</v>
+        <v>1.2</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1433</v>
+        <v>0.845</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5098</v>
+        <v>0.355</v>
       </c>
       <c r="V16" t="n">
-        <v>2.5235</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>3.1674</v>
+        <v>0.3219</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.6439</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.7116</v>
+        <v>2.4633</v>
       </c>
       <c r="E17" t="n">
-        <v>3.4381</v>
+        <v>4.1112</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.7265</v>
+        <v>-1.6478</v>
       </c>
       <c r="G17" t="n">
         <v>0.2574</v>
@@ -1780,13 +1780,13 @@
         <v>2.0158</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.2238</v>
+        <v>-0.4721</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6063</v>
+        <v>0.0668</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.6175</v>
+        <v>-0.5389</v>
       </c>
       <c r="V17" t="n">
         <v>1.5785</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. MORTE MONTANES</t>
+          <t>J. SABATE PRATS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1879</v>
+        <v>0.3657</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6776</v>
+        <v>0.4847</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.4897</v>
+        <v>-0.119</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.643</v>
+        <v>0.7176</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1969</v>
+        <v>-0.2024</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.8399</v>
+        <v>0.92</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0819</v>
+        <v>2.2122</v>
       </c>
       <c r="K20" t="n">
-        <v>2.9536</v>
+        <v>0.8111</v>
       </c>
       <c r="L20" t="n">
-        <v>-2.8717</v>
+        <v>1.401</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.7249</v>
+        <v>-1.4946</v>
       </c>
       <c r="N20" t="n">
-        <v>-2.7567</v>
+        <v>-1.0136</v>
       </c>
       <c r="O20" t="n">
-        <v>0.0318</v>
+        <v>-0.481</v>
       </c>
       <c r="P20" t="n">
-        <v>0.1833</v>
+        <v>-0.1833</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.7489</v>
+        <v>-1.8326</v>
       </c>
       <c r="R20" t="n">
-        <v>2.9321</v>
+        <v>1.6493</v>
       </c>
       <c r="S20" t="n">
-        <v>1.3702</v>
+        <v>-0.4906</v>
       </c>
       <c r="T20" t="n">
-        <v>2.0672</v>
+        <v>-0.2168</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6969</v>
+        <v>-0.2738</v>
       </c>
       <c r="V20" t="n">
-        <v>1.2774</v>
+        <v>0.3219</v>
       </c>
       <c r="W20" t="n">
-        <v>1.2774</v>
+        <v>0.3219</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. SABATE PRATS</t>
+          <t>G. VOLPATO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3424</v>
+        <v>0.342</v>
       </c>
       <c r="E21" t="n">
-        <v>0.004</v>
+        <v>0.9277</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.3463</v>
+        <v>-0.5857</v>
       </c>
       <c r="G21" t="n">
-        <v>0.7176</v>
+        <v>-1.7147</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.2024</v>
+        <v>-0.4265</v>
       </c>
       <c r="I21" t="n">
-        <v>0.92</v>
+        <v>-1.2881</v>
       </c>
       <c r="J21" t="n">
-        <v>2.2122</v>
+        <v>-0.2047</v>
       </c>
       <c r="K21" t="n">
-        <v>0.8111</v>
+        <v>-0.3593</v>
       </c>
       <c r="L21" t="n">
-        <v>1.401</v>
+        <v>0.1546</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.4946</v>
+        <v>-1.51</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.0136</v>
+        <v>-0.0673</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.481</v>
+        <v>-1.4427</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.1833</v>
+        <v>1.6493</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.8326</v>
+        <v>-0.9163</v>
       </c>
       <c r="R21" t="n">
-        <v>1.6493</v>
+        <v>2.5656</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.1986</v>
+        <v>0.0958</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6976</v>
+        <v>0.7817</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5011</v>
+        <v>-0.6859</v>
       </c>
       <c r="V21" t="n">
-        <v>0.3219</v>
+        <v>0.3115</v>
       </c>
       <c r="W21" t="n">
-        <v>0.3219</v>
+        <v>1.267</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.9554</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.5676</v>
+        <v>-0.2762</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.4629</v>
+        <v>-0.2705</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.1048</v>
+        <v>-0.0057</v>
       </c>
       <c r="G22" t="n">
         <v>-0.1835</v>
@@ -2170,13 +2170,13 @@
         <v>0.1833</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2454</v>
+        <v>0.046</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0732</v>
+        <v>0.2655</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3186</v>
+        <v>-0.2195</v>
       </c>
       <c r="V22" t="n">
         <v>-0.3219</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>G. VOLPATO</t>
+          <t>P. MORTE MONTANES</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.0917</v>
+        <v>-0.6294</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.13</v>
+        <v>-0.6686</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.9616</v>
+        <v>0.0392</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.7147</v>
+        <v>-2.643</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.4265</v>
+        <v>0.1969</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.2881</v>
+        <v>-2.8399</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.2047</v>
+        <v>0.0819</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.3593</v>
+        <v>2.9536</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1546</v>
+        <v>-2.8717</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.51</v>
+        <v>-2.7249</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.0673</v>
+        <v>-2.7567</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.4427</v>
+        <v>0.0318</v>
       </c>
       <c r="P23" t="n">
-        <v>1.6493</v>
+        <v>0.1833</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.9163</v>
+        <v>-2.7489</v>
       </c>
       <c r="R23" t="n">
-        <v>2.5656</v>
+        <v>2.9321</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.3379</v>
+        <v>0.553</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.276</v>
+        <v>0.721</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.0618</v>
+        <v>-0.168</v>
       </c>
       <c r="V23" t="n">
-        <v>0.3115</v>
+        <v>1.2774</v>
       </c>
       <c r="W23" t="n">
-        <v>1.267</v>
+        <v>1.2774</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.9554</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A. IGBINS DAVID</t>
+          <t>M. MARIA VENTURA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.6208</v>
+        <v>-1.6281</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.5289</v>
+        <v>-1.7541</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.0918</v>
+        <v>0.1259</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.0546</v>
+        <v>-1.6692</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.4933</v>
+        <v>0.8758</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.5613</v>
+        <v>-2.545</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.3984</v>
+        <v>-1.4279</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.44</v>
+        <v>0.4118</v>
       </c>
       <c r="L24" t="n">
-        <v>0.0417</v>
+        <v>-1.8397</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.6563</v>
+        <v>-0.2413</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.0532</v>
+        <v>0.464</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.603</v>
+        <v>-0.7053</v>
       </c>
       <c r="P24" t="n">
-        <v>0.3665</v>
+        <v>-0.3665</v>
       </c>
       <c r="Q24" t="n">
         <v>-0.9163</v>
       </c>
       <c r="R24" t="n">
-        <v>1.2828</v>
+        <v>0.5498</v>
       </c>
       <c r="S24" t="n">
-        <v>1.0674</v>
+        <v>0.4076</v>
       </c>
       <c r="T24" t="n">
-        <v>1.4088</v>
+        <v>0.5901</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3414</v>
+        <v>-0.1825</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.6231</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0.6231</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>M. MARIA VENTURA</t>
+          <t>A. IGBINS DAVID</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.1089</v>
+        <v>-2.3361</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.2349</v>
+        <v>-1.2982</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1259</v>
+        <v>-1.0379</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.6692</v>
+        <v>-3.0546</v>
       </c>
       <c r="H25" t="n">
-        <v>0.8758</v>
+        <v>-1.4933</v>
       </c>
       <c r="I25" t="n">
-        <v>-2.545</v>
+        <v>-1.5613</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.4279</v>
+        <v>-0.3984</v>
       </c>
       <c r="K25" t="n">
-        <v>0.4118</v>
+        <v>-0.44</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.8397</v>
+        <v>0.0417</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.2413</v>
+        <v>-2.6563</v>
       </c>
       <c r="N25" t="n">
-        <v>0.464</v>
+        <v>-1.0532</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.7053</v>
+        <v>-1.603</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.3665</v>
+        <v>0.3665</v>
       </c>
       <c r="Q25" t="n">
         <v>-0.9163</v>
       </c>
       <c r="R25" t="n">
-        <v>0.5498</v>
+        <v>1.2828</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.0732</v>
+        <v>0.352</v>
       </c>
       <c r="T25" t="n">
-        <v>0.1094</v>
+        <v>0.6395</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.1825</v>
+        <v>-0.2875</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>-0.6231</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>0.6231</v>
       </c>
     </row>
     <row r="26">
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-3.0728</v>
+        <v>-2.337</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.1884</v>
+        <v>-0.8038</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.8844</v>
+        <v>-1.5333</v>
       </c>
       <c r="G26" t="n">
         <v>-1.3307</v>
@@ -2482,13 +2482,13 @@
         <v>1.8326</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.0799</v>
+        <v>-0.3441</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.497</v>
+        <v>-0.1123</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.5829</v>
+        <v>-0.2317</v>
       </c>
       <c r="V26" t="n">
         <v>-1.5785</v>
@@ -2515,19 +2515,19 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>10.3107</v>
+        <v>11.5929</v>
       </c>
       <c r="E27" t="n">
-        <v>15.6061</v>
+        <v>15.606</v>
       </c>
       <c r="F27" t="n">
-        <v>-5.2953</v>
+        <v>-4.0133</v>
       </c>
       <c r="G27" t="n">
         <v>-1.1281</v>
       </c>
       <c r="H27" t="n">
-        <v>0.7934999999999999</v>
+        <v>0.7934999999999994</v>
       </c>
       <c r="I27" t="n">
         <v>-1.9215</v>
@@ -2560,13 +2560,13 @@
         <v>19.242</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.003800000000000248</v>
+        <v>1.2782</v>
       </c>
       <c r="T27" t="n">
-        <v>4.0124</v>
+        <v>4.0123</v>
       </c>
       <c r="U27" t="n">
-        <v>-4.0159</v>
+        <v>-2.734</v>
       </c>
       <c r="V27" t="n">
         <v>4.1124</v>
